--- a/Reports.xlsx
+++ b/Reports.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,25 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Info_icon</t>
+          <t>Share_icon</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Share_icon</t>
+          <t>Save_icon</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Save_icon</t>
+          <t>Download_icon</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>Download_icon</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
@@ -471,27 +466,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>The 3-month rolling average for DEEPINTENT_CLICKS and DEEPINTENT_IMPRESSIONS for Cardizor shows no activity from September 2023 to January 2024, with all values at zero. Starting February 2024, DEEPINTENT_CLICKS and DEEPINTENT_IMPRESSIONS begin to increase steadily, peaking in July 2024 at 842.67 clicks and 1,566,063.33 impressions. After this peak, both metrics show a gradual decline through December 2024, with clicks at 355.33 and impressions at 1,365,468.67.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WITH MonthlyDeepIntentData AS ( SELECT
+  DATE_TRUNC('month', "MONTH_YEAR") AS "MonthStartDate",
+  SUM(COALESCE("DEEPINTENT_CLICKS", 0)) AS "MonthlyDeepIntentClicks",
+  SUM(COALESCE("DEEPINTENT_IMPRESSIONS", 0)) AS "MonthlyDeepIntentImpressions"
+FROM mmm."Segmentation_Master_Dataset"
+WHERE "PHYSICIAN_NPI_ID" IS NOT NULL AND "PHYSICIAN_NPI_ID" &lt;&gt; '' AND "PHYSICIAN_NPI_ID" &lt;&gt; '9999999999' AND "PHYSICIAN_SEGMENT" IS NOT NULL AND "PHYSICIAN_SEGMENT" &lt;&gt; '' AND UPPER("PHYSICIAN_SEGMENT") &lt;&gt; 'UNKNOWN'
+GROUP BY DATE_TRUNC('month', "MONTH_YEAR") ) SELECT "MonthStartDate", AVG("MonthlyDeepIntentClicks") OVER (
+ORDER BY "MonthStartDate" ROWS BETWEEN 2 PRECEDING AND CURRENT ROW) AS "3MonthRollingAvgDeepIntentClicks", AVG("MonthlyDeepIntentImpressions") OVER (
+ORDER BY "MonthStartDate" ROWS BETWEEN 2 PRECEDING AND CURRENT ROW) AS "3MonthRollingAvgDeepIntentImpressions"
+FROM MonthlyDeepIntentData
+ORDER BY "MonthStartDate";</t>
         </is>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -503,25 +510,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>Campaign  DEEPINTENT_CLICKS_14284  experienced  an  11.25%  growth  in  clicks  compared  to  the  previous  month,  increasing  from  320  to  356</t>
         </is>
       </c>
       <c r="D3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
       </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -535,25 +539,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>Over  the  last  6  months,  CARDIZOR_NRx  demonstrated  strong</t>
         </is>
       </c>
       <c r="D4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
       </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -567,40 +568,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The  month-over-month  percentage  change  in  total  digital  promotions  varies  significantly  across  specialty  groups.  For  example,  the  CARD  group  experienced  dramatic  fluctuations,  including  a  sharp</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WITH MonthlySpecialtyPromotions AS ( SELECT
-  "PRIMARY_SPECIALTY_GROUP",
-  "MONTH_YEAR",
-  SUM("TOTAL_DIGITAL_PROMOTIONS") AS CurrentMonthPromotions
-FROM "mmm"."Segmentation_Master_Dataset"
-WHERE "PHYSICIAN_NPI_ID" IS NOT NULL AND "PHYSICIAN_NPI_ID" &lt;&gt; '' AND "PHYSICIAN_NPI_ID" &lt;&gt; '9999999999' AND "PHYSICIAN_SEGMENT" IS NOT NULL AND "PHYSICIAN_SEGMENT" &lt;&gt; '' AND UPPER("PHYSICIAN_SEGMENT") &lt;&gt; 'UNKNOWN' AND "PRIMARY_SPECIALTY_GROUP" IS NOT NULL AND "PRIMARY_SPECIALTY_GROUP" &lt;&gt; ''
-GROUP BY "PRIMARY_SPECIALTY_GROUP", "MONTH_YEAR" ), LaggedPromotions AS ( SELECT "PRIMARY_SPECIALTY_GROUP", "MONTH_YEAR", CurrentMonthPromotions, LAG(CurrentMonthPromotions, 1, 0) OVER (PARTITION BY "PRIMARY_SPECIALTY_GROUP"
-ORDER BY "MONTH_YEAR") AS PreviousMonthPromotions
-FROM MonthlySpecialtyPromotions ) SELECT "PRIMARY_SPECIALTY_GROUP", "MONTH_YEAR", CurrentMonthPromotions AS TotalDigitalPromotionsCurrentMonth, PreviousMonthPromotions AS TotalDigitalPromotionsPreviousMonth, CASE WHEN PreviousMonthPromotions = 0 THEN NULL -- Avoid division by zero; indicates no promotions in the previous month ELSE ROUND( ((CurrentMonthPromotions - PreviousMonthPromotions) * 100.0) / PreviousMonthPromotions, 2 ) END AS MoMPercentageChange
-FROM LaggedPromotions
-ORDER BY "PRIMARY_SPECIALTY_GROUP", "MONTH_YEAR";</t>
+          <t>The provided data does not contain month-over-month (MoM) activity volumes for digital promotions, so a MoM percentage change cannot be calculated. The available data represents a single snapshot of activity volumes by segment and channel.</t>
         </is>
       </c>
       <c r="D5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
@@ -614,27 +597,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>Rahway and Coon Rapids experienced the highest growth in virtual calls over the last quarter, with a remarkable 700% increase. Valdosta and Fort Smith followed closely, each achieving a 600% growth, while Richfield and Westminster saw a 500% rise. Other cities like Sayre and Mesa showed a 400% increase, with Lewisburg and North Syracuse rounding out the list at 300%.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WITH latest AS ( SELECT
+  MAX(CAST("MONTH_YEAR" AS date)) AS max_data_date
+FROM "mmm"."Segmentation_Master_Dataset" ), quarters AS ( SELECT DATE_TRUNC('quarter', max_data_date) AS current_quarter_start, DATE_TRUNC('quarter', max_data_date) - INTERVAL '3 months' AS last_completed_quarter_start, DATE_TRUNC('quarter', max_data_date) AS last_completed_quarter_end, DATE_TRUNC('quarter', max_data_date) - INTERVAL '6 months' AS prior_completed_quarter_start, DATE_TRUNC('quarter', max_data_date) - INTERVAL '3 months' AS prior_completed_quarter_end
+FROM latest ), last_qtr_data AS ( SELECT s."CITY", SUM(COALESCE(s."VIRTUAL_CALLS", 0)) AS virtual_calls_last_qtr
+FROM "mmm"."Segmentation_Master_Dataset" s CROSS
+JOIN quarters q
+WHERE s."MONTH_YEAR" &gt;= q.last_completed_quarter_start AND s."MONTH_YEAR" &lt; q.last_completed_quarter_end
+GROUP BY s."CITY" ), prior_qtr_data AS ( SELECT s."CITY", SUM(COALESCE(s."VIRTUAL_CALLS", 0)) AS virtual_calls_prior_qtr
+FROM "mmm"."Segmentation_Master_Dataset" s CROSS
+JOIN quarters q
+WHERE s."MONTH_YEAR" &gt;= q.prior_completed_quarter_start AND s."MONTH_YEAR" &lt; q.prior_completed_quarter_end
+GROUP BY s."CITY" ), growth_calc AS ( SELECT COALESCE(lqd."CITY", pqd."CITY") AS city_name, COALESCE(lqd.virtual_calls_last_qtr, 0) AS last_qtr_calls, COALESCE(pqd.virtual_calls_prior_qtr, 0) AS prior_qtr_calls, CASE WHEN COALESCE(pqd.virtual_calls_prior_qtr, 0) &gt; 0 THEN ((COALESCE(lqd.virtual_calls_last_qtr, 0) - COALESCE(pqd.virtual_calls_prior_qtr, 0)) * 100.0) / COALESCE(pqd.virtual_calls_prior_qtr, 0) WHEN COALESCE(lqd.virtual_calls_last_qtr, 0) &gt; 0 AND COALESCE(pqd.virtual_calls_prior_qtr, 0) = 0 THEN 100.0 ELSE 0.0 END AS virtual_calls_growth_pct
+FROM last_qtr_data lqd FULL OUTER
+JOIN prior_qtr_data pqd
+ON lqd."CITY" = pqd."CITY" ) SELECT city_name AS "City", last_qtr_calls AS "LastQuarterVirtualCalls", prior_qtr_calls AS "PriorQuarterVirtualCalls", virtual_calls_growth_pct AS "VirtualCallsGrowthPercentage"
+FROM growth_calc
+WHERE virtual_calls_growth_pct &gt; 0
+ORDER BY virtual_calls_growth_pct DESC
+LIMIT 10;</t>
         </is>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -646,416 +649,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>No response</t>
+          <t>The Cardizor No Prescriptions Segment is most responsive to Digital Promotions, with 24.4% of its total incremental impact attributed to this channel. The Cardizor High Share Segment and Cardizor Low Share High Volume Segment also show moderate responsiveness, contributing 6.7% and 5.8% respectively to their overall impact.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SQL query not available.</t>
         </is>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Which HCP segments are driving the most growth</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Display changes in average samples shipped per city.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Display changes in average samples shipped per physician tier.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Show changes on total speaker attendees over the last four quarters.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>How do face-to-face calls (F2F_CALLS) and virtual calls (VIRTUAL_CALLS) relate to new Cardizor prescriptions (CARDIZOR_NRX) across physician segments (PHYSICIAN_SEGMENT) over time?</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The  provided  data  does  not  differentiate  between  face-to-face  and  virtual  calls,  nor  does  it  contain  time-series  information  to  analyze  trends  over  time.  Therefore,  I  cannot  directly  answer  how  F2F_CALLS  and  VIRTUAL_CALLS  relate  to  new  Cardizor  prescriptions  across  physician  segments  over  time.  The  available  data  only  shows  the  overall  'Calls'  contribution  impact  by  segment.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SQL query not available.</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Visualize the relative market share distribution of Cardizor and its competitors based on total TRx over the past year, showing how each brand contributes to the overall total.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Please provide the top 20 HCPs prescribing Cardizor, including the number of new prescriptions each has written, along with details of their respective various marketing channels.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Identify which specialty had the fastest TRx growth trend.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Which campaign (DeepIntent, Medscape, Relevate) showed increasing engagement over time?</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Identify the competitor with the fastest TRx growth rate from Sep 2022 to Sep 2023.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Determine correlation between Tier level and total F2F calls.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>There  is  a</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Which states show underperformance relative to their physician count?</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>No response</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
